--- a/output/graficos_nacionales/plot_nacional_e_medianeta_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_medianeta_a_2019.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -15688,7 +15688,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -15826,7 +15826,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -15872,7 +15872,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_medianeta_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_medianeta_a_2019.xlsx
@@ -2143,7 +2143,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:44</t>
+    <t xml:space="preserve">2026-09-07 12:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_medianeta_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_medianeta_a_2019.xlsx
@@ -2143,7 +2143,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:50</t>
+    <t xml:space="preserve">2026-09-08 10:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
